--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kumar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE582626-AB4D-41AE-AD17-ACB52EBA5D80}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="696" yWindow="1404" windowWidth="12708" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1066,9 @@
       <c r="L7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="16"/>
+      <c r="M7" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE582626-AB4D-41AE-AD17-ACB52EBA5D80}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3989ADE6-CD73-457D-83E9-159A77F7C83F}"/>
   <bookViews>
-    <workbookView xWindow="696" yWindow="1404" windowWidth="12708" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1072,25 +1072,47 @@
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>60</v>
+      </c>
+      <c r="D8" s="14">
+        <v>140</v>
+      </c>
+      <c r="E8" s="14">
+        <v>40</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>40</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3989ADE6-CD73-457D-83E9-159A77F7C83F}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7E85E8C-45F5-481D-8CB1-6FFC53AC4C5E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1116,25 +1116,47 @@
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14">
+        <v>130</v>
+      </c>
+      <c r="E9" s="14">
+        <v>50</v>
+      </c>
+      <c r="F9" s="14">
+        <v>420</v>
+      </c>
+      <c r="G9" s="14">
+        <v>7</v>
+      </c>
+      <c r="H9" s="14">
+        <v>30</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7E85E8C-45F5-481D-8CB1-6FFC53AC4C5E}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3D4BCAD-3A88-40CC-A927-BCDA4C748D07}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1160,25 +1160,47 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>60</v>
+      </c>
+      <c r="D10" s="14">
+        <v>130</v>
+      </c>
+      <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>240</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>35</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>445</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3D4BCAD-3A88-40CC-A927-BCDA4C748D07}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94C160A7-49F8-4920-A571-C36317334175}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1204,135 +1204,267 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>40</v>
+      </c>
+      <c r="F11" s="14">
+        <v>360</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>40</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B12" s="14">
+        <v>440</v>
+      </c>
+      <c r="C12" s="14">
+        <v>50</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>40</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>50</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>150</v>
+      </c>
+      <c r="E13" s="14">
+        <v>50</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>50</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>140</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>420</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>50</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>290</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B15" s="14">
+        <v>430</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>40</v>
+      </c>
+      <c r="F15" s="14">
+        <v>240</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>50</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14">
+        <v>130</v>
+      </c>
+      <c r="E16" s="14">
+        <v>40</v>
+      </c>
+      <c r="F16" s="14">
+        <v>360</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>50</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94C160A7-49F8-4920-A571-C36317334175}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6EFE20A-BB49-4695-BFE7-2D706E4788C5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1468,47 +1468,91 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>130</v>
+      </c>
+      <c r="E17" s="14">
+        <v>50</v>
+      </c>
+      <c r="F17" s="14">
+        <v>360</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>50</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>130</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>240</v>
+      </c>
+      <c r="G18" s="14">
+        <v>4</v>
+      </c>
+      <c r="H18" s="14">
+        <v>40</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6EFE20A-BB49-4695-BFE7-2D706E4788C5}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EECE5DCA-B536-4057-B5C8-774F631F9CCC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1202,7 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>51</v>
@@ -1237,13 +1243,13 @@
         <v>400</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N11" s="17"/>
     </row>
@@ -1328,7 +1334,7 @@
         <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>51</v>
@@ -1358,24 +1364,24 @@
         <v>7</v>
       </c>
       <c r="H14" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N14" s="17"/>
     </row>
@@ -1402,15 +1408,15 @@
         <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>940</v>
+        <v>890</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
@@ -1463,7 +1469,7 @@
         <v>50</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N16" s="17"/>
     </row>
@@ -1556,91 +1562,179 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>40</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>40</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>240</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>30</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B21" s="14">
+        <v>490</v>
+      </c>
+      <c r="C21" s="14">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14">
+        <v>0</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <v>100</v>
+      </c>
+      <c r="G21" s="14">
+        <v>2</v>
+      </c>
+      <c r="H21" s="14">
+        <v>60</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>750</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>50</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>50</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>50</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EECE5DCA-B536-4057-B5C8-774F631F9CCC}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B406112-0F2A-4643-83B6-D93AF9271EE6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1738,113 +1738,223 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>140</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>20</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>610</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>830</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>45</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>50</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>695</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>745</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>130</v>
+      </c>
+      <c r="E25" s="14">
+        <v>20</v>
+      </c>
+      <c r="F25" s="14">
+        <v>250</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>140</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>25</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>675</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B406112-0F2A-4643-83B6-D93AF9271EE6}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E99A55B2-69E3-4D10-A1CD-C0D63B3E5BBE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1217,7 +1217,7 @@
         <v>420</v>
       </c>
       <c r="C11" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D11" s="14">
         <v>120</v>
@@ -1236,11 +1236,11 @@
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>980</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>59</v>
@@ -1261,7 +1261,7 @@
         <v>440</v>
       </c>
       <c r="C12" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D12" s="14">
         <v>120</v>
@@ -1280,11 +1280,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1305,7 +1305,7 @@
         <v>480</v>
       </c>
       <c r="C13" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D13" s="14">
         <v>150</v>
@@ -1324,11 +1324,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1030</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1349,7 +1349,7 @@
         <v>420</v>
       </c>
       <c r="C14" s="14">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D14" s="14">
         <v>140</v>
@@ -1368,11 +1368,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>1060</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>59</v>
@@ -1393,7 +1393,7 @@
         <v>430</v>
       </c>
       <c r="C15" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D15" s="14">
         <v>120</v>
@@ -1412,11 +1412,11 @@
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>860</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
@@ -1437,7 +1437,7 @@
         <v>420</v>
       </c>
       <c r="C16" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D16" s="14">
         <v>130</v>
@@ -1456,11 +1456,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1000</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>49</v>
@@ -1481,7 +1481,7 @@
         <v>420</v>
       </c>
       <c r="C17" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D17" s="14">
         <v>130</v>
@@ -1500,11 +1500,11 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>1010</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
@@ -1525,7 +1525,7 @@
         <v>480</v>
       </c>
       <c r="C18" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D18" s="14">
         <v>130</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>950</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>490</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>49</v>
@@ -1569,7 +1569,7 @@
         <v>480</v>
       </c>
       <c r="C19" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D19" s="14">
         <v>120</v>
@@ -1588,11 +1588,11 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>59</v>
@@ -1613,7 +1613,7 @@
         <v>480</v>
       </c>
       <c r="C20" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>120</v>
@@ -1632,11 +1632,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
@@ -1657,7 +1657,7 @@
         <v>490</v>
       </c>
       <c r="C21" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D21" s="14">
         <v>0</v>
@@ -1676,11 +1676,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>49</v>
@@ -1701,7 +1701,7 @@
         <v>420</v>
       </c>
       <c r="C22" s="14">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D22" s="14">
         <v>120</v>
@@ -1720,11 +1720,11 @@
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>59</v>
@@ -1958,47 +1958,91 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>140</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>580</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>160</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>250</v>
+      </c>
+      <c r="G29" s="14">
+        <v>5</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E99A55B2-69E3-4D10-A1CD-C0D63B3E5BBE}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA9362C6-6445-4499-99DD-FE893EAF1CD8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2046,25 +2046,47 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B30" s="14">
+        <v>460</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>100</v>
+      </c>
+      <c r="E30" s="14">
+        <v>20</v>
+      </c>
+      <c r="F30" s="14">
+        <v>100</v>
+      </c>
+      <c r="G30" s="14">
+        <v>2</v>
+      </c>
+      <c r="H30" s="14">
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>760</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA9362C6-6445-4499-99DD-FE893EAF1CD8}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01CCC01F-A666-4807-AB1B-5E7BA190383F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2090,25 +2090,47 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>840</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01CCC01F-A666-4807-AB1B-5E7BA190383F}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A8289A2-6F11-4D1C-A09E-1D85C8F010B6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2134,25 +2134,47 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>300</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A8289A2-6F11-4D1C-A09E-1D85C8F010B6}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04A6E2CB-6387-4A5B-8FD7-363B6B239976}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G32" s="14">
         <v>5</v>
@@ -2160,11 +2160,11 @@
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>790</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>59</v>
@@ -2178,25 +2178,47 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>44824</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>160</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>350</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>0</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04A6E2CB-6387-4A5B-8FD7-363B6B239976}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD5DC0B-8B9E-4E1F-B3B7-8C05877CB777}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
-        <v>44824</v>
+        <v>46287</v>
       </c>
       <c r="B33" s="14">
         <v>420</v>
@@ -2222,25 +2222,47 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>0</v>
+      </c>
+      <c r="E34" s="14">
+        <v>0</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>0</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>770</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">

--- a/12619672.xlsx
+++ b/12619672.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/086da1e279199750/Desktop/demo/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD5DC0B-8B9E-4E1F-B3B7-8C05877CB777}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{71548BFE-4034-498A-9CBD-BA9509800866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0D986E5-B105-43D1-AC98-07ACE0974545}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2266,25 +2266,47 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>30</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
